--- a/basedatos_partidas/salida/descompuestos/CT-08-04-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-020.xlsx
@@ -539,10 +539,10 @@
         <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="H10" t="n">
-        <v>4.42</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="11">
@@ -591,10 +591,10 @@
         <v>0.32</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="13">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.41</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -776,10 +776,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>11.46</v>
+        <v>13.92</v>
       </c>
       <c r="H23" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="24">
@@ -795,7 +795,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>11.57</v>
+        <v>14.06</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-04-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos de madera y laminados</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-04-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-020.xlsx
@@ -485,7 +485,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piso de tabla de madera maciza clavada sobre rastreles fijados al contrapiso, con cámara ventilada. Es la solución tradicional y la más duradera, ya que la madera maciza admite varios lijados a lo largo de su vida. Incluye la aplicación de preservante en los rastreles y en la cara inferior de la tabla, el replanteo y nivelación del rastrelado, la ventilación de la cámara mediante rejillas perimetrales, el clavado oculto de la tabla, la junta perimetral de dilatación y el remate. No incluye el lijado y barnizado final, que se valora aparte. La madera la elige el cliente y se presupuesta aparte. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
+          <t xml:space="preserve">Piso de tabla de madera maciza clavada sobre rastreles fijados al afirmado, con cámara ventilada. Es la solución tradicional y la más duradera, ya que la madera maciza admite varios lijados a lo largo de su vida. Incluye la aplicación de preservante en los rastreles y en la cara inferior de la tabla, el replanteo y nivelación del rastrelado, la ventilación de la cámara mediante rejillas perimetrales, el clavado oculto de la tabla, la junta perimetral de dilatación y el remate. No incluye el lijado y barnizado final, que se valora aparte. La madera la elige el cliente y se presupuesta aparte. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
 </t>
         </is>
       </c>
